--- a/05_Figures/F06_prediction/proteins/acute/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/d_1rm_legpress/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -146,9 +146,6 @@
     <t xml:space="preserve">ATAD3A</t>
   </si>
   <si>
-    <t xml:space="preserve">CAT</t>
-  </si>
-  <si>
     <t xml:space="preserve">HPCAL1</t>
   </si>
   <si>
@@ -161,417 +158,390 @@
     <t xml:space="preserve">SH3BGRL3</t>
   </si>
   <si>
-    <t xml:space="preserve">STOM</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMED5</t>
   </si>
   <si>
     <t xml:space="preserve">GPC1</t>
   </si>
   <si>
+    <t xml:space="preserve">HSPB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XRCC6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABHD14B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPNA1</t>
+  </si>
+  <si>
     <t xml:space="preserve">NGLY1</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMD11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABHD14B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLNC</t>
+    <t xml:space="preserve">PSMF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMYD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TXNDC17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPZ1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECHDC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLUD1</t>
   </si>
   <si>
     <t xml:space="preserve">HPRT1</t>
   </si>
   <si>
-    <t xml:space="preserve">TXNDC17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPNA1</t>
-  </si>
-  <si>
     <t xml:space="preserve">LDHD</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS19</t>
+    <t xml:space="preserve">MYO1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NACA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUTF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIP10</t>
   </si>
   <si>
     <t xml:space="preserve">UBE2D1</t>
   </si>
   <si>
-    <t xml:space="preserve">XRCC6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPZ1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLUD1</t>
+    <t xml:space="preserve">GATD3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL37</t>
   </si>
   <si>
     <t xml:space="preserve">PRMT5</t>
   </si>
   <si>
-    <t xml:space="preserve">PRPS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRIP10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NACA</t>
+    <t xml:space="preserve">AKT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLNB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USP14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH4A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYB5A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FYCO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HADH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM1</t>
   </si>
   <si>
     <t xml:space="preserve">PITHD1</t>
   </si>
   <si>
-    <t xml:space="preserve">SPTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECHDC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATD3B</t>
+    <t xml:space="preserve">PLN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPP1R3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XIRP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADVL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIMP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP2M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP1A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5PO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNA1S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPNS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAVIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCDC22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNPY2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DCAF8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DNAJA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4G2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EZR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCLM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTM2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H3-3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILK</t>
   </si>
   <si>
     <t xml:space="preserve">MPP1</t>
   </si>
   <si>
-    <t xml:space="preserve">PPP1R3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMYD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLVRB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYB5A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ERAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUTF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USP14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH4A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP1B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNA1S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CARM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLNB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FYCO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3-3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HADH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO1C</t>
+    <t xml:space="preserve">MRPL22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTIF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFA12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIPSNAP3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTF1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PABPC4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKFB1</t>
   </si>
   <si>
     <t xml:space="preserve">PNPO</t>
   </si>
   <si>
-    <t xml:space="preserve">PRKAA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB1A</t>
+    <t xml:space="preserve">PPCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PREB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTPN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPLP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMM50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SKP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLMAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRP14</t>
   </si>
   <si>
     <t xml:space="preserve">SUMO2</t>
   </si>
   <si>
-    <t xml:space="preserve">XIRP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACADVL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIMP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMPD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP2M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2B4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5PO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLMH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CA14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPNS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAVIN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCDC22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHCHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNPY2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCAF8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNAJA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4G2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EZR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GDI2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GGCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSD17B10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAVS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MTIF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKFB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP1R7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PREB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PTPN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPLP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAMM50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SERBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SKP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLMAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRP14</t>
-  </si>
-  <si>
     <t xml:space="preserve">SYNJ2BP</t>
   </si>
   <si>
@@ -587,19 +557,16 @@
     <t xml:space="preserve">TUBB2A</t>
   </si>
   <si>
+    <t xml:space="preserve">TXN2</t>
+  </si>
+  <si>
     <t xml:space="preserve">UBA1</t>
   </si>
   <si>
-    <t xml:space="preserve">UBE2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBE3A</t>
-  </si>
-  <si>
     <t xml:space="preserve">UBXN6</t>
   </si>
   <si>
-    <t xml:space="preserve">UQCC3</t>
+    <t xml:space="preserve">UQCRFS1</t>
   </si>
   <si>
     <t xml:space="preserve">USP5</t>
@@ -992,16 +959,16 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.81098486050524</v>
+        <v>-1.83700277093809</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.513009642383935</v>
+        <v>-0.493278502292245</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1025,29 +992,21 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.81098486050524</v>
+        <v>-1.83700277093809</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.513009642383935</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.940298507462687</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.870646766169154</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.664486816747217</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.67712045984447</v>
-      </c>
+        <v>-0.493278502292245</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1071,2206 +1030,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.254965134826995</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.226036871078134</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.265877915998736</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.32357366590373</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-1.11973358519535</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.0679681767623175</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-1.10496215927014</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.893204282542164</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.363160367687462</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.19126017183505</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.368799037718029</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.714624209858503</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.504762758729352</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.16900181291441</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.0387451399893244</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.854483840891196</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.0932798987159271</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.807979859666406</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.75281122532661</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.23754789052693</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.36659779191153</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.759149144055121</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.90234835091713</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.563941206636212</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-1.5401660476268</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.0619496949062592</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.58119578671036</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.535194171416687</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.564068457740566</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.255691202700916</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.235159737215181</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.8130434675859</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.806044842046647</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.213210937181382</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.537580187169543</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0.33729108798887</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-2.26372904658283</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.725571194226349</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.19955946811462</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-1.27686371350169</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.859382992723186</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.12873433318135</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.634250493127233</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.541425632988443</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-1.00321985245601</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-1.03263639461058</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.670003324001882</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.522195709364073</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.3624118203639</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.707608366593556</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-1.39252720828129</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-0.966924205788545</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.31233685953067</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.893170233082915</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.48266461823063</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-2.53404107889803</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.704900216266327</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.377001596022578</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.0782116088772483</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.49517786895641</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.357145469254223</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.429031017106286</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.949138603619588</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.763695552690762</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.510896732192835</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.5866647796423</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-1.20665695980189</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.0979806257416067</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.806943311072618</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.756948082982152</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.933725346205674</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-0.896401122161489</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.67316480821205</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.0718426029547197</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.722059776994242</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-1.22101098675677</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.497674671570849</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0.415220934261006</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>0.0358860154906396</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-1.92257755528502</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.48208963785922</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-1.75270632076646</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-1.08707567898072</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-0.62861274414966</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-1.60964361557219</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.777379797628211</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.542148123369051</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.648989223285308</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-2.47028023939397</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.470310964483096</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>0.205866362330342</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.50624883587796</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.4661750948443</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-2.1418406171792</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>0.0811748062456022</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-1.06602951640819</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>0.137245304914545</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0.455576053898916</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.768162131767018</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.547007880728109</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.18031958520545</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.213511246894245</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-0.910797432504889</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.745755321876179</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>0.16117895909503</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.137655301509615</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.436962397514262</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.590780956907997</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>0.319237770465356</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.28354470402537</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.454110050247348</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-2.1179584392177</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-0.0721576527439913</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.892710415924298</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.16662530477277</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-1.13761402945395</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.191435939424359</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.639896230228362</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.9489048436244</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.465650308743664</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-2.094066703286</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.02378816093232</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-1.47016697314371</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.656484819056191</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.656709525627534</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>0.36012088334854</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.0581797804027973</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.388194694072179</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.499221829871675</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>0.0447544191111952</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.723715232058139</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.79041477917182</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.529626039220629</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.0720773274023072</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0.0467235878935903</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-2.02629643085065</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.60450505621556</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.210043440423107</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.844199505416251</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.205484388775822</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.593218697445612</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.352972867423483</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.17625924776617</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>0.072638260829931</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-0.52772117895913</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.89226191579528</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.851837345749958</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.00315214149075049</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.237029019555978</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.038280362308621</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.715437024845434</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.94060916952866</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.17126330374792</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>0.11098038444882</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.611411596307899</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.67665945490061</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-1.15596394337319</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.10298131624255</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-3.38178555600954</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>0.485084793674638</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.567841479209929</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.484146977336471</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>0.0346553101345349</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-1.84784898828785</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.386467739798755</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.493123808873589</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.811977766909541</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.10757513218602</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.451283331140042</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.636068514719301</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.08726168439963</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.256512058081059</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.387151868206949</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.702272234210664</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.10480931259403</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.00146311457307924</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.298449125029517</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-2.20817870155037</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.549688367614351</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>0.0847204876634167</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.339381308392182</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.793298200461576</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-1.48609144224402</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-0.147724646201763</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>0.281057724563235</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.427591223525376</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.258784624472023</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.537882421465274</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.268154936118214</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.0255403349010819</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.0833648652613439</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>0.175039585920837</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-1.78035544274722</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>0.0354200615162441</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.486948806186963</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.763414251418712</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.558579657161946</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.609481428201354</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.31601603671092</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.5357524823698</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3313,7 +1072,7 @@
         <v>54</v>
       </c>
       <c r="E2" t="n">
-        <v>47.8722567109116</v>
+        <v>52.6634665451214</v>
       </c>
     </row>
     <row r="3">
@@ -3330,7 +1089,7 @@
         <v>83</v>
       </c>
       <c r="E3" t="n">
-        <v>15.0692352124443</v>
+        <v>12.2730088228728</v>
       </c>
     </row>
     <row r="4">
@@ -3347,7 +1106,7 @@
         <v>90</v>
       </c>
       <c r="E4" t="n">
-        <v>3.86028223020833</v>
+        <v>6.81249305952257</v>
       </c>
     </row>
     <row r="5">
@@ -3364,7 +1123,7 @@
         <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>45.3140283514646</v>
+        <v>41.7866508315522</v>
       </c>
     </row>
     <row r="6">
@@ -3381,7 +1140,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>106.791460437731</v>
+        <v>106.673812975294</v>
       </c>
     </row>
     <row r="7">
@@ -3398,7 +1157,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>23.7333474744399</v>
+        <v>36.3482689543293</v>
       </c>
     </row>
     <row r="8">
@@ -3415,7 +1174,7 @@
         <v>25</v>
       </c>
       <c r="E8" t="n">
-        <v>6.04573575215749</v>
+        <v>12.9901172399532</v>
       </c>
     </row>
     <row r="9">
@@ -3432,7 +1191,7 @@
         <v>72</v>
       </c>
       <c r="E9" t="n">
-        <v>7.11607713028917</v>
+        <v>6.00205724528484</v>
       </c>
     </row>
     <row r="10">
@@ -3449,7 +1208,7 @@
         <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>0.913409052866555</v>
+        <v>3.85061977183113</v>
       </c>
     </row>
     <row r="11">
@@ -3466,7 +1225,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>52.4175700630293</v>
+        <v>51.2896426191045</v>
       </c>
     </row>
     <row r="12">
@@ -3483,7 +1242,7 @@
         <v>62</v>
       </c>
       <c r="E12" t="n">
-        <v>47.5407573338822</v>
+        <v>44.8992856826847</v>
       </c>
     </row>
     <row r="13">
@@ -3500,7 +1259,7 @@
         <v>25</v>
       </c>
       <c r="E13" t="n">
-        <v>42.8606922904447</v>
+        <v>34.7665873754238</v>
       </c>
     </row>
     <row r="14">
@@ -3517,7 +1276,7 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>82.2309961395309</v>
+        <v>86.4788004905997</v>
       </c>
     </row>
     <row r="15">
@@ -3534,7 +1293,7 @@
         <v>5</v>
       </c>
       <c r="E15" t="n">
-        <v>50.2870366316453</v>
+        <v>47.9967292515469</v>
       </c>
     </row>
     <row r="16">
@@ -3551,7 +1310,7 @@
         <v>89</v>
       </c>
       <c r="E16" t="n">
-        <v>44.4281181661934</v>
+        <v>42.721935393563</v>
       </c>
     </row>
   </sheetData>
@@ -3627,10 +1386,10 @@
         <v>40</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -3644,10 +1403,10 @@
         <v>41</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.733333333333333</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -3661,10 +1420,10 @@
         <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
@@ -3678,10 +1437,10 @@
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="8">
@@ -3695,10 +1454,10 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="9">
@@ -3712,10 +1471,10 @@
         <v>45</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="10">
@@ -3729,10 +1488,10 @@
         <v>46</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="11">
@@ -3746,10 +1505,10 @@
         <v>47</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.666666666666667</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12">
@@ -3763,10 +1522,10 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>0.666666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -3780,10 +1539,10 @@
         <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.666666666666667</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="14">
@@ -3797,10 +1556,10 @@
         <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -3814,10 +1573,10 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -3831,10 +1590,10 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -3848,10 +1607,10 @@
         <v>53</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.533333333333333</v>
+        <v>0.466666666666667</v>
       </c>
     </row>
     <row r="18">
@@ -3865,10 +1624,10 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.533333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="19">
@@ -3882,10 +1641,10 @@
         <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.533333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20">
@@ -3899,10 +1658,10 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.533333333333333</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="21">
@@ -3916,10 +1675,10 @@
         <v>57</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22">
@@ -3933,10 +1692,10 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="23">
@@ -3950,10 +1709,10 @@
         <v>59</v>
       </c>
       <c r="D23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="24">
@@ -3967,10 +1726,10 @@
         <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>0.466666666666667</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="25">
@@ -3984,10 +1743,10 @@
         <v>61</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -4001,10 +1760,10 @@
         <v>62</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="27">
@@ -4018,10 +1777,10 @@
         <v>63</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="28">
@@ -4035,10 +1794,10 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E28" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="29">
@@ -4052,10 +1811,10 @@
         <v>65</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.466666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="30">
@@ -4069,10 +1828,10 @@
         <v>66</v>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="31">
@@ -4086,10 +1845,10 @@
         <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="32">
@@ -4103,10 +1862,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="33">
@@ -4120,10 +1879,10 @@
         <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="34">
@@ -4137,10 +1896,10 @@
         <v>70</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="35">
@@ -4154,10 +1913,10 @@
         <v>71</v>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="36">
@@ -4171,10 +1930,10 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.4</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="37">
@@ -4239,10 +1998,10 @@
         <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.333333333333333</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="41">
@@ -4290,10 +2049,10 @@
         <v>79</v>
       </c>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="44">
@@ -4307,10 +2066,10 @@
         <v>80</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="45">
@@ -4324,10 +2083,10 @@
         <v>81</v>
       </c>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E45" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="46">
@@ -4341,10 +2100,10 @@
         <v>82</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.266666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="47">
@@ -4375,10 +2134,10 @@
         <v>84</v>
       </c>
       <c r="D48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="49">
@@ -4392,10 +2151,10 @@
         <v>85</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="50">
@@ -4409,10 +2168,10 @@
         <v>86</v>
       </c>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="51">
@@ -4426,10 +2185,10 @@
         <v>87</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="52">
@@ -4443,10 +2202,10 @@
         <v>88</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="53">
@@ -4460,10 +2219,10 @@
         <v>89</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -4630,10 +2389,10 @@
         <v>99</v>
       </c>
       <c r="D63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="64">
@@ -4647,10 +2406,10 @@
         <v>100</v>
       </c>
       <c r="D64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="65">
@@ -4664,10 +2423,10 @@
         <v>101</v>
       </c>
       <c r="D65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="66">
@@ -4681,10 +2440,10 @@
         <v>102</v>
       </c>
       <c r="D66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E66" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="67">
@@ -4698,10 +2457,10 @@
         <v>103</v>
       </c>
       <c r="D67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="68">
@@ -4715,10 +2474,10 @@
         <v>104</v>
       </c>
       <c r="D68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="69">
@@ -4732,10 +2491,10 @@
         <v>105</v>
       </c>
       <c r="D69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="70">
@@ -4749,10 +2508,10 @@
         <v>106</v>
       </c>
       <c r="D70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="71">
@@ -4766,10 +2525,10 @@
         <v>107</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="72">
@@ -4783,10 +2542,10 @@
         <v>108</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="73">
@@ -4800,10 +2559,10 @@
         <v>109</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>0.133333333333333</v>
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="74">
@@ -6095,193 +3854,6 @@
         <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="s">
-        <v>186</v>
-      </c>
-      <c r="D150" t="n">
-        <v>1</v>
-      </c>
-      <c r="E150" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="s">
-        <v>187</v>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="s">
-        <v>188</v>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="s">
-        <v>189</v>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="s">
-        <v>190</v>
-      </c>
-      <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="s">
-        <v>191</v>
-      </c>
-      <c r="D155" t="n">
-        <v>1</v>
-      </c>
-      <c r="E155" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="s">
-        <v>192</v>
-      </c>
-      <c r="D156" t="n">
-        <v>1</v>
-      </c>
-      <c r="E156" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="s">
-        <v>193</v>
-      </c>
-      <c r="D157" t="n">
-        <v>1</v>
-      </c>
-      <c r="E157" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="s">
-        <v>194</v>
-      </c>
-      <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="s">
-        <v>195</v>
-      </c>
-      <c r="D159" t="n">
-        <v>1</v>
-      </c>
-      <c r="E159" t="n">
-        <v>0.0666666666666667</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="s">
-        <v>196</v>
-      </c>
-      <c r="D160" t="n">
-        <v>1</v>
-      </c>
-      <c r="E160" t="n">
         <v>0.0666666666666667</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/acute/d_1rm_legpress/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/acute/d_1rm_legpress/spls/c_data/results.xlsx
@@ -995,7 +995,7 @@
         <v>1900</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.83700277093809</v>
@@ -1003,10 +1003,18 @@
       <c r="I3" t="n">
         <v>-0.493278502292245</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.950248756218905</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.880597014925373</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.648106272655093</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.658802721669855</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1030,6 +1038,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.239567161281682</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.190661421590293</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.297422250142944</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.3483050431945</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.02892465880704</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.287113022772357</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.78385803002761</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.955312324661471</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.227568493079374</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.13708001969313</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.710806807067378</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.664258041252033</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.631202778710505</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.406668278417218</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0402712676806449</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.619625544218506</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.114120390120733</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.770699305573973</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.6194119273695</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.245710398080436</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.28811837353869</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-0.804433944433316</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.08716449881306</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.54385662164706</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-1.47523599816563</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.119756162296829</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.898068845770042</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.476568118824103</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.545926756864673</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-0.105170206563661</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.276742445884413</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.882177026037643</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.77684355809936</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.194603395112446</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.590945084420038</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.344383036181839</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-2.16836634817428</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.639723842353586</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.865370210853733</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-1.31211642414879</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.809318470931226</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.15322485403706</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.199046978636418</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.14277662266517</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.692395296536072</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-1.44088082301818</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.512444595035107</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.58287249947919</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.02102108246373</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.672490739451671</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-1.48763574864483</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-0.880249179734758</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.1814512854331</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.799779499679683</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.391367406401269</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-2.30352996554965</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.04241280176065</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.437745750034413</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.145897210265042</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.47710542452805</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.283823116910311</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.428215478809709</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.04967136866768</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.967172383293903</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.508693001554574</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.673242350706666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-1.15785024427995</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0.0872388427381214</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.729804289436717</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.714938550557471</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.994529046924719</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-0.705353630030889</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.42063952070177</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.0720539444785916</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.133148871412692</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-1.20895976014202</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.232277392912212</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0.343776299280864</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.0122919188936454</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.967834299802241</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.38097653125095</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-2.04260220082195</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-1.68504996600186</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-0.737816439230407</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-1.49403081363842</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.808620333829912</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.626675976574767</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.603702330622942</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-2.37736733285151</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.475610360783854</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0.182846127255322</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.53478314039323</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-2.53556812748608</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-2.10520863869466</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.0675040975749053</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.995818031268372</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0.412686391256194</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0.436673973840031</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.757518874438649</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.495443111562177</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.26515856635328</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.122044485355468</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-0.807980220803199</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.359197971692867</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.142649072484702</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.0542218478434988</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.499238461544688</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.564328614996798</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>0.288400123558804</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.21265108713501</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.232973313005268</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-2.04000467305217</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-0.0342516178966117</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.987704626452084</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-0.788446892606756</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.906426147274092</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.200982237824906</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.234356485047923</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-0.486731516879376</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.655084922234176</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-1.68278746247475</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.88665137019673</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-1.37639897546139</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.457387552876826</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.369109687177605</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.227380187562585</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.187825707899979</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.325982285604395</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.264713279172592</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.00253917628416123</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.757109051622377</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.953203374523627</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.444193593700861</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.236223215538234</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.143491331806207</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-1.9520719444792</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.43185481687628</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.390126180679274</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.954722786046329</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.235732727966216</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.601489368800805</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.30724343568045</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.10977805720769</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.0453392297024044</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.26776050924398</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.812878139584923</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.852527569154764</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.0181669695689944</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.171910708506969</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.118036555146617</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.619348303415485</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.847094437168709</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.044024407095</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.373617375692326</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.00892156143361</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.774534264993432</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.867631769583485</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.51792944780462</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-3.08116059457956</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.197319503633106</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.699852808258042</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.290484140877887</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.0888525147562259</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-1.76623602962925</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.397304633766057</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.520409264704234</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.749859333891425</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.14939223371113</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.408783609140169</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.632658083085541</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-1.2242424369278</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.643852601940454</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.340073153676007</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.837229652008008</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.56374622093752</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.0353951295576825</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.258764300942083</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.40235492700033</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.479614184493295</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.278193801850937</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.583762094947889</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.522295336747387</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-2.12921638806763</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>-0.13019148057213</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.216866821565158</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.473093841695061</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.305109879101133</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.39843608444513</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.246291517775562</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.00356998584004131</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.165411128963873</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.126589101417349</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.67699300990589</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.00742028538918604</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.134980781183432</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.909232107549995</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.526981824226697</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.456779176277416</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.35823493952573</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.57133330500812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
